--- a/output/отфильтрованные_разметки_единиц.xlsx
+++ b/output/отфильтрованные_разметки_единиц.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,69 +905,6 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>133</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>T24_000000_t35Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>8</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>на конец года тысяч рублей</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>133</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>T24_000000_t35Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>на конец года тысяч рублей</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>133</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>T24_000000_t35Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>10</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>на конец года тысяч рублей</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/отфильтрованные_разметки_единиц.xlsx
+++ b/output/отфильтрованные_разметки_единиц.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -844,15 +844,15 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T24_000000_t26Ved14.xlsx</t>
+          <t>T24_000000_t28Ved14.xlsx</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -873,33 +873,12 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>тысяч рублей</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>98</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>9</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>тысяч рублей</t>
         </is>

--- a/output/отфильтрованные_разметки_единиц.xlsx
+++ b/output/отфильтрованные_разметки_единиц.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,190 +445,190 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14.xlsx</t>
+          <t>M25_000000_t23FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t23FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t23FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T24_000000_t23Ved14mo8.xlsx</t>
+          <t>M25_000000_t23FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T24_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23FsVed14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T24_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T24_000000_t25Ved14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
@@ -638,18 +638,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T24_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
@@ -659,18 +659,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T24_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
@@ -680,60 +680,60 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T24_000000_t25Ved14mo8.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>M25_000000_t23OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
@@ -743,95 +743,95 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T24_000000_t25OpfVed14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T24_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T24_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T24_000000_t25FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>на конец года тысяч рублей</t>
+          <t>тысяч рублей</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T24_000000_t26Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -844,15 +844,15 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -865,20 +865,272 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>T24_000000_t28Ved14.xlsx</t>
+          <t>M25_000000_t23Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>78</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>78</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>85</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>85</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>86</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>86</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M25_000000_t25Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>88</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>88</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>100</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>100</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M25_000000_t26Ved14mo8.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>14</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>109</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M25_000000_t28Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>109</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M25_000000_t28Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>11</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>тысяч рублей</t>
         </is>

--- a/output/отфильтрованные_разметки_единиц.xlsx
+++ b/output/отфильтрованные_разметки_единиц.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -491,7 +491,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -533,7 +533,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -554,7 +554,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -575,7 +575,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M25_000000_t23FsVed14.xlsx</t>
+          <t>M25_000000_t23Ved14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="n">

--- a/output/отфильтрованные_разметки_единиц.xlsx
+++ b/output/отфильтрованные_разметки_единиц.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,15 +445,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -466,15 +466,15 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
@@ -487,15 +487,15 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -508,15 +508,15 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14mo8.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -529,11 +529,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14mo8.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -550,11 +550,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S25_000000_t25Ved14mo8.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -571,15 +571,15 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S25_000000_t25OpfVed14.xlsx</t>
+          <t>S25_000000_t23-прVed14.xlsx</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -592,15 +592,15 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S25_000000_t25OpfVed14.xlsx</t>
+          <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -613,15 +613,15 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S25_000000_t25OpfVed14.xlsx</t>
+          <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -634,15 +634,15 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S25_000000_t25FsVed14.xlsx</t>
+          <t>S25_000000_t25Ved14.xlsx</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -655,15 +655,15 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S25_000000_t25FsVed14.xlsx</t>
+          <t>S25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -676,15 +676,15 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S25_000000_t25FsVed14.xlsx</t>
+          <t>S25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
@@ -697,15 +697,15 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>S25_000000_t26Ved14.xlsx</t>
+          <t>S25_000000_t25Ved14mo8.xlsx</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -718,15 +718,15 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S25_000000_t26Ved14.xlsx</t>
+          <t>S25_000000_t25OpfVed14.xlsx</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -739,20 +739,167 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>111</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S25_000000_t25OpfVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S25_000000_t25OpfVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>S25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S25_000000_t25FsVed14.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S25_000000_t26Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S25_000000_t26Ved14.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>тысяч рублей</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>138</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>S25_000000_t28Ved14.xlsx</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C23" t="n">
         <v>11</v>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>тысяч рублей</t>
         </is>
